--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambatomanga.xlsx
@@ -420,12 +420,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,12 +506,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -581,12 +569,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -627,12 +609,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -650,12 +626,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -673,12 +643,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -811,12 +775,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -926,12 +884,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -994,12 +946,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>0.2</v>
       </c>
     </row>
     <row r="29">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambatomanga.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D2">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>52.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3">
@@ -417,8 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>18.9</v>
       </c>
     </row>
     <row r="4">
@@ -434,14 +440,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>10.3</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="5">
@@ -457,14 +463,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>11.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -480,14 +480,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>16.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7">
@@ -503,8 +503,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>28.4</v>
       </c>
     </row>
     <row r="8">
@@ -520,14 +526,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9">
@@ -543,14 +549,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>63</v>
-      </c>
-      <c r="E9">
-        <v>78.8</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -566,8 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>25.9</v>
       </c>
     </row>
     <row r="11">
@@ -583,14 +589,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D11">
         <v>7</v>
       </c>
       <c r="E11">
-        <v>8.800000000000001</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="12">
@@ -606,7 +612,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -623,7 +629,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -640,8 +646,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>18.5</v>
       </c>
     </row>
     <row r="15">
@@ -657,14 +669,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D15">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>46.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -680,14 +692,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D16">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E16">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="17">
@@ -703,14 +715,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D17">
-        <v>62</v>
+        <v>289</v>
       </c>
       <c r="E17">
-        <v>7.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="18">
@@ -726,14 +738,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D18">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -749,14 +761,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D19">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E19">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -772,8 +784,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>57</v>
+      </c>
+      <c r="E20">
+        <v>10.8</v>
       </c>
     </row>
     <row r="21">
@@ -789,14 +807,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E21">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -807,19 +825,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D22">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="23">
@@ -835,14 +853,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>418</v>
-      </c>
-      <c r="E23">
-        <v>71.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -858,14 +870,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="E24">
-        <v>3.2</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="25">
@@ -881,8 +893,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>16</v>
+      </c>
+      <c r="E25">
+        <v>7.5</v>
       </c>
     </row>
     <row r="26">
@@ -898,14 +916,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D26">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E26">
-        <v>17.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="27">
@@ -928,7 +946,7 @@
         <v>19</v>
       </c>
       <c r="E27">
-        <v>3.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -944,31 +962,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>25</v>
-      </c>
-      <c r="E29">
-        <v>4.3</v>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>38</v>
+      </c>
+      <c r="E28">
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
